--- a/verification/cases/roundtrip/rich_text/init.xlsx
+++ b/verification/cases/roundtrip/rich_text/init.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19814FF6-833C-4935-B3DD-54EC62162CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13720" yWindow="3720" windowWidth="10720" windowHeight="16060" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -481,7 +482,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -668,7 +669,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -680,7 +681,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -714,6 +714,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1038,12 +1046,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1051,7 +1059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1059,7 +1067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1067,7 +1075,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1075,7 +1083,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1083,47 +1091,47 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17">
+    <row r="7" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16">
+    <row r="8" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="17">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="18">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
@@ -1131,24 +1139,24 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A12" s="11" t="s">
         <v>22</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="18">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A13" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>26</v>
       </c>
       <c r="B15" t="s">
